--- a/data/source/history.xlsx
+++ b/data/source/history.xlsx
@@ -1419,17 +1419,17 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>После падения Кушанского царства в Средней Азии усилились кочевые племена эфталитов (иногда называемых «белыми гуннами»), создавшие к V в. обширную державу, включавшую территории современного Узбекистана, Афганистана и части Индии; эфталиты успешно противостояли Сасанидскому Ирану. В середине VI в. (551–555 гг.) государство эфталитов было разгромлено в результате союза Тюркского каганата (образованного тюркоязычными племенами во главе с родом Ашина) и Сасанидского Ирана. С этого момента территория современного Узбекистана вошла в состав Тюркского каганата — крупнейшего кочевого государства раннего Средневековья, простиравшегося от Маньчжурии до Чёрного моря. При тюрках согдийские города-государства (Самарканд, Пенджикент, Бухара) сохраняли значительную автономию во внутренних делах, продолжая играть роль главных посредников в караванной торговле по Великому шёлковому пути между Китаем и Византией/Ираном. В 603 г. каганат разделился на Западный и Восточный; земли Средней Азии вошли в Западно-тюркский каганат, просуществовавший до арабского завоевания в начале VIII в.</t>
+          <t>После падения Кушанского царства в Средней Азии усилились кочевые племена эфталитов (иногда называемых «белыми гуннами»), создавшие к V в. обширную державу, включавшую территории современного Узбекистана, Афганистана и части Индии; эфталиты успешно противостояли Сасанидскому Ирану. В середине VI в. (551–555 гг.; в некоторых источниках — 557–560 гг.) государство эфталитов было разгромлено в результате союза Тюркского каганата (образованного тюркоязычными племенами во главе с родом Ашина) и Сасанидского Ирана. С этого момента территория современного Узбекистана вошла в состав Тюркского каганата — крупнейшего кочевого государства раннего Средневековья, простиравшегося от Маньчжурии до Чёрного моря. При тюрках согдийские города-государства (Самарканд, Пенджикент, Бухара) сохраняли значительную автономию во внутренних делах, продолжая играть роль главных посредников в караванной торговле по Великому шёлковому пути между Китаем и Византией/Ираном. В 603 г. каганат разделился на Западный и Восточный; земли Средней Азии вошли в Западно-тюркский каганат, просуществовавший до арабского завоевания в начале VIII в.</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Kushon podsholigi qulaganidan so‘ng O‘rta Osiyoda ko‘chmanchi eftalit qabilalari (ba’zan «oq gunnlar» deb ataladi) kuchayib, V asrga kelib hozirgi O‘zbekiston, Afg‘oniston va Hindistonning bir qismi yerlarini o‘z ichiga olgan keng davlat barpo etdi; eftalitlar Sosoniylar Eroniga muvaffaqiyatli qarshilik ko‘rsatgan. VI asr o‘rtalarida (551–555-yillar) eftalitlar davlati Turk xoqonligi (Ashina urug‘i boshchiligidagi turkiy tilli qabilalar tomonidan tuzilgan) va Sosoniylar Eroni ittifoqi natijasida tor-mor etildi. Shu paytdan boshlab hozirgi O‘zbekiston hududi ilk o‘rta asrlarning eng yirik ko‘chmanchi davlati — Manchjuriyadan Qora dengizgacha cho‘zilgan Turk xoqonligi tarkibiga kirdi. Turklar davrida sug‘diy shahar-davlatlari (Samarqand, Panjikent, Buxoro) ichki ishlarda katta avtonomiyani saqlab qolgan holda, Xitoy va Vizantiya/Eron o‘rtasidagi Buyuk ipak yo‘li karvon savdosida asosiy vositachi rolini davom ettirdi. 603-yilda xoqonlik G‘arbiy va Sharqiy qismlarga bo‘lindi; O‘rta Osiyo yerlari VIII asr boshidagi arab bosqinigacha mavjud bo‘lgan G‘arbiy turk xoqonligi tarkibiga kirdi.</t>
+          <t>Kushon podsholigi qulaganidan so‘ng O‘rta Osiyoda ko‘chmanchi eftalit qabilalari (ba’zan «oq gunnlar» deb ataladi) kuchayib, V asrga kelib hozirgi O‘zbekiston, Afg‘oniston va Hindistonning bir qismi yerlarini o‘z ichiga olgan keng davlat barpo etdi; eftalitlar Sosoniylar Eroniga muvaffaqiyatli qarshilik ko‘rsatgan. VI asr o‘rtalarida (551–555-yillar; ayrim manbalarda — 557–560-yillar) eftalitlar davlati Turk xoqonligi (Ashina urug‘i boshchiligidagi turkiy tilli qabilalar tomonidan tuzilgan) va Sosoniylar Eroni ittifoqi natijasida tor-mor etildi. Shu paytdan boshlab hozirgi O‘zbekiston hududi ilk o‘rta asrlarning eng yirik ko‘chmanchi davlati — Manchjuriyadan Qora dengizgacha cho‘zilgan Turk xoqonligi tarkibiga kirdi. Turklar davrida sug‘diy shahar-davlatlari (Samarqand, Panjikent, Buxoro) ichki ishlarda katta avtonomiyani saqlab qolgan holda, Xitoy va Vizantiya/Eron o‘rtasidagi Buyuk ipak yo‘li karvon savdosida asosiy vositachi rolini davom ettirdi. 603-yilda xoqonlik G‘arbiy va Sharqiy qismlarga bo‘lindi; O‘rta Osiyo yerlari VIII asr boshidagi arab bosqinigacha mavjud bo‘lgan G‘arbiy turk xoqonligi tarkibiga kirdi.</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>After the fall of the Kushan Empire, the nomadic Hephthalite tribes (sometimes called «White Huns») grew strong in Central Asia, building by the 5th century a vast state covering the territory of modern Uzbekistan, Afghanistan and part of India; the Hephthalites successfully resisted Sasanian Iran. In the mid-6th century (551–555 CE), the Hephthalite state was crushed by an alliance of the Turkic Khaganate (formed by Turkic-speaking tribes led by the Ashina clan) and Sasanian Iran. From that point, the territory of modern Uzbekistan became part of the Turkic Khaganate, the largest nomadic state of the early Middle Ages, stretching from Manchuria to the Black Sea. Under the Turks, the Sogdian city-states (Samarkand, Panjikent, Bukhara) retained considerable autonomy in internal affairs while continuing to serve as key intermediaries in Silk Road caravan trade between China and Byzantium/Iran. In 603 the khaganate split into a Western and an Eastern part; the lands of Central Asia became part of the Western Turkic Khaganate, which lasted until the Arab conquest in the early 8th century.</t>
+          <t>After the fall of the Kushan Empire, the nomadic Hephthalite tribes (sometimes called «White Huns») grew strong in Central Asia, building by the 5th century a vast state covering the territory of modern Uzbekistan, Afghanistan and part of India; the Hephthalites successfully resisted Sasanian Iran. In the mid-6th century (551–555 CE; some sources give 557–560), the Hephthalite state was crushed by an alliance of the Turkic Khaganate (formed by Turkic-speaking tribes led by the Ashina clan) and Sasanian Iran. From that point, the territory of modern Uzbekistan became part of the Turkic Khaganate, the largest nomadic state of the early Middle Ages, stretching from Manchuria to the Black Sea. Under the Turks, the Sogdian city-states (Samarkand, Panjikent, Bukhara) retained considerable autonomy in internal affairs while continuing to serve as key intermediaries in Silk Road caravan trade between China and Byzantium/Iran. In 603 the khaganate split into a Western and an Eastern part; the lands of Central Asia became part of the Western Turkic Khaganate, which lasted until the Arab conquest in the early 8th century.</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -2349,32 +2349,32 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>В начале XVI в. предводитель узбекских кочевых племён Мухаммад Шейбани-хан завоевал Мавераннахр, положив конец правлению Тимуридов. С этого времени этноним «узбеки» закрепился за оседлым населением региона, а Бухара стала столицей нового государства.</t>
+          <t>В начале XVI в. предводитель узбекских кочевых племён Мухаммад Шейбани-хан завоевал Мавераннахр, положив конец правлению Тимуридов. С этого времени этноним «узбеки» закрепился за оседлым населением региона, а столицей нового государства стал Самарканд (с середины XVI в. — Бухара).</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>XVI asr boshida o‘zbek ko‘chmanchi qabilalari sardori Muhammad Shayboniyxon Movarounnahrni zabt etib, Temuriylar hukmronligiga barham berdi. Shu davrdan boshlab «o‘zbek» etnonimi mintaqaning o‘troq aholisiga mustahkamlanib qoldi, Buxoro esa yangi davlatning poytaxtiga aylandi.</t>
+          <t>XVI asr boshida o‘zbek ko‘chmanchi qabilalari sardori Muhammad Shayboniyxon Movarounnahrni zabt etib, Temuriylar hukmronligiga barham berdi. Shu davrdan boshlab «o‘zbek» etnonimi mintaqaning o‘troq aholisiga mustahkamlanib qoldi, yangi davlatning poytaxti Samarqand (XVI asr o‘rtasidan — Buxoro) bo‘ldi.</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>In the early 16th century, the leader of the Uzbek nomadic tribes, Muhammad Shaybani Khan, conquered Mawarannahr, ending Timurid rule. From this time the ethnonym «Uzbek» became attached to the settled population of the region, and Bukhara became the capital of the new state.</t>
+          <t>In the early 16th century, the leader of the Uzbek nomadic tribes, Muhammad Shaybani Khan, conquered Mawarannahr, ending Timurid rule. From this time the ethnonym «Uzbek» became attached to the settled population of the region, and Samarkand (from the mid-16th century, Bukhara) became the capital of the new state.</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Название «узбеки» первоначально относилось к кочевым тюрко-монгольским племенам, обитавшим в степях к северу от Аральского моря и Сырдарьи (улус Шибана, потомка Джучи, сына Чингисхана); со временем эти племена консолидировались в единую этнополитическую общность. В 1500–1507 гг. хан Мухаммад Шейбани, возглавивший объединённые узбекские кочевые племена, разгромил ослабевших Тимуридов и завоевал Мавераннахр, Хорезм и часть Хорасана, основав государство Шейбанидов (1500–1598 гг.) со столицей в Бухаре (позднее также важную роль играл Самарканд). Приход узбекских племён ознаменовал важный этап этнической истории региона: постепенно смешавшись с оседлым тюрко-персидским населением Мавераннахра, кочевые узбеки передали ему своё имя — с этого времени и население Мавераннахра, и сам регион всё чаще стали именоваться «узбекскими». При Шейбанидах продолжалось развитие городской культуры, строились медресе (в частности, знаменитые медресе на площади Регистан в Самарканде получили окончательное оформление позже, при Аштарханидах, но традиция была заложена и в это время), торговля с Россией, Индией и Ираном. Одновременно государство было ослаблено постоянными войнами с Сефевидским Ираном (из-за религиозных разногласий — узбекские правители придерживались суннизма, персы — шиизма) и внутренними усобицами между членами династии. В конце XVI в. династия Шейбанидов пресеклась, и власть перешла к новой династии — Аштарханидам (Джанидам).</t>
+          <t>Название «узбеки» первоначально относилось к кочевым тюрко-монгольским племенам, обитавшим в степях к северу от Аральского моря и Сырдарьи (улус Шибана, потомка Джучи, сына Чингисхана); со временем эти племена консолидировались в единую этнополитическую общность. В 1500–1507 гг. хан Мухаммад Шейбани, возглавивший объединённые узбекские кочевые племена, разгромил ослабевших Тимуридов и завоевал Мавераннахр, Хорезм и часть Хорасана, основав государство Шейбанидов (1500–1598 гг.) со столицей сначала в Самарканде, а с середины XVI в. — в Бухаре. Приход узбекских племён ознаменовал важный этап этнической истории региона: постепенно смешавшись с оседлым тюрко-персидским населением Мавераннахра, кочевые узбеки передали ему своё имя — с этого времени и население Мавераннахра, и сам регион всё чаще стали именоваться «узбекскими». При Шейбанидах продолжалось развитие городской культуры, строились медресе (в частности, знаменитые медресе на площади Регистан в Самарканде получили окончательное оформление позже, при Аштарханидах, но традиция была заложена и в это время), торговля с Россией, Индией и Ираном. Одновременно государство было ослаблено постоянными войнами с Сефевидским Ираном (из-за религиозных разногласий — узбекские правители придерживались суннизма, персы — шиизма) и внутренними усобицами между членами династии. В конце XVI в. династия Шейбанидов пресеклась, и власть перешла к новой династии — Аштарханидам (Джанидам).</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>«O‘zbek» nomi dastlab Orol dengizi va Sirdaryodan shimolda joylashgan dashtlarda yashagan ko‘chmanchi turk-mo‘g‘ul qabilalariga (Chingizxon o‘g‘li Jo‘chining avlodi Shayboniy ulusi) tegishli bo‘lgan; vaqt o‘tishi bilan bu qabilalar yagona etnosiyosiy jamoaga birlashdi. 1500–1507-yillarda birlashgan o‘zbek ko‘chmanchi qabilalari boshlig‘i Muhammad Shayboniyxon zaiflashgan Temuriylarni tor-mor etib, Movarounnahr, Xorazm va Xurosonning bir qismini zabt etdi, poytaxti Buxoro (keyinroq Samarqand ham muhim rol o‘ynagan) bo‘lgan Shayboniylar davlatiga (1500–1598-yillar) asos soldi. O‘zbek qabilalarining kelishi mintaqa etnik tarixining muhim bosqichini belgiladi: asta-sekin Movarounnahrning o‘troq turk-fors aholisi bilan aralashib, ko‘chmanchi o‘zbeklar unga o‘z nomini berdi — shu vaqtdan boshlab Movarounnahr aholisi ham, mintaqaning o‘zi ham tobora ko‘proq «o‘zbek» deb atala boshladi. Shayboniylar davrida shahar madaniyati rivoji davom etdi, madrasalar qurildi (xususan, Samarqanddagi Registon maydonidagi mashhur madrasalar keyinroq, Ashtarxoniylar davrida yakuniy shaklga keldi, biroq an’ana aynan shu davrda boshlangan edi), Rossiya, Hindiston va Eron bilan savdo rivojlandi. Shu bilan birga davlat Safaviylar Eroni bilan doimiy urushlar (diniy kelishmovchiliklar tufayli — o‘zbek hukmdorlari sunniylikka, forslar shialikka amal qilgan) va sulola a’zolari o‘rtasidagi ichki nizolar tufayli zaiflashdi. XVI asr oxirida Shayboniylar sulolasi barham topdi, hokimiyat yangi sulola — Ashtarxoniylar (Joniylar)ga o‘tdi.</t>
+          <t>«O‘zbek» nomi dastlab Orol dengizi va Sirdaryodan shimolda joylashgan dashtlarda yashagan ko‘chmanchi turk-mo‘g‘ul qabilalariga (Chingizxon o‘g‘li Jo‘chining avlodi Shayboniy ulusi) tegishli bo‘lgan; vaqt o‘tishi bilan bu qabilalar yagona etnosiyosiy jamoaga birlashdi. 1500–1507-yillarda birlashgan o‘zbek ko‘chmanchi qabilalari boshlig‘i Muhammad Shayboniyxon zaiflashgan Temuriylarni tor-mor etib, Movarounnahr, Xorazm va Xurosonning bir qismini zabt etdi, poytaxti avval Samarqand, XVI asr o‘rtasidan esa Buxoro bo‘lgan Shayboniylar davlatiga (1500–1598-yillar) asos soldi. O‘zbek qabilalarining kelishi mintaqa etnik tarixining muhim bosqichini belgiladi: asta-sekin Movarounnahrning o‘troq turk-fors aholisi bilan aralashib, ko‘chmanchi o‘zbeklar unga o‘z nomini berdi — shu vaqtdan boshlab Movarounnahr aholisi ham, mintaqaning o‘zi ham tobora ko‘proq «o‘zbek» deb atala boshladi. Shayboniylar davrida shahar madaniyati rivoji davom etdi, madrasalar qurildi (xususan, Samarqanddagi Registon maydonidagi mashhur madrasalar keyinroq, Ashtarxoniylar davrida yakuniy shaklga keldi, biroq an’ana aynan shu davrda boshlangan edi), Rossiya, Hindiston va Eron bilan savdo rivojlandi. Shu bilan birga davlat Safaviylar Eroni bilan doimiy urushlar (diniy kelishmovchiliklar tufayli — o‘zbek hukmdorlari sunniylikka, forslar shialikka amal qilgan) va sulola a’zolari o‘rtasidagi ichki nizolar tufayli zaiflashdi. XVI asr oxirida Shayboniylar sulolasi barham topdi, hokimiyat yangi sulola — Ashtarxoniylar (Joniylar)ga o‘tdi.</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>The name «Uzbek» originally referred to the nomadic Turco-Mongol tribes living in the steppes north of the Aral Sea and the Syr Darya (the Shibanid ulus, descendants of Jochi, son of Genghis Khan); over time these tribes consolidated into a single ethno-political community. In 1500–1507, Khan Muhammad Shaybani, leading the united Uzbek nomadic tribes, crushed the weakened Timurids and conquered Mawarannahr, Khorezm and part of Khorasan, founding the Shaybanid state (1500–1598) with its capital at Bukhara (Samarkand also later played an important role). The arrival of the Uzbek tribes marked an important stage in the region's ethnic history: gradually mixing with the settled Turko-Persian population of Mawarannahr, the nomadic Uzbeks passed on their name to it — from this time both the population of Mawarannahr and the region itself increasingly came to be called «Uzbek». Under the Shaybanids, urban culture continued to develop, madrasas were built (the famous madrasas on the Registan Square in Samarkand, for instance, took their final form somewhat later, under the Ashtarkhanids, but the tradition began in this period), and trade with Russia, India and Iran flourished. At the same time, the state was weakened by constant wars with Safavid Iran (over religious differences — Uzbek rulers were Sunni, the Persians Shia) and internal strife among dynasty members. At the end of the 16th century the Shaybanid dynasty died out, and power passed to a new dynasty — the Ashtarkhanids (Janids).</t>
+          <t>The name «Uzbek» originally referred to the nomadic Turco-Mongol tribes living in the steppes north of the Aral Sea and the Syr Darya (the Shibanid ulus, descendants of Jochi, son of Genghis Khan); over time these tribes consolidated into a single ethno-political community. In 1500–1507, Khan Muhammad Shaybani, leading the united Uzbek nomadic tribes, crushed the weakened Timurids and conquered Mawarannahr, Khorezm and part of Khorasan, founding the Shaybanid state (1500–1598) with its capital first at Samarkand and, from the mid-16th century, at Bukhara. The arrival of the Uzbek tribes marked an important stage in the region's ethnic history: gradually mixing with the settled Turko-Persian population of Mawarannahr, the nomadic Uzbeks passed on their name to it — from this time both the population of Mawarannahr and the region itself increasingly came to be called «Uzbek». Under the Shaybanids, urban culture continued to develop, madrasas were built (the famous madrasas on the Registan Square in Samarkand, for instance, took their final form somewhat later, under the Ashtarkhanids, but the tradition began in this period), and trade with Russia, India and Iran flourished. At the same time, the state was weakened by constant wars with Safavid Iran (over religious differences — Uzbek rulers were Sunni, the Persians Shia) and internal strife among dynasty members. At the end of the 16th century the Shaybanid dynasty died out, and power passed to a new dynasty — the Ashtarkhanids (Janids).</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>После пресечения династии Шейбанидов в 1599 г. власть в Бухарском ханстве перешла к династии Аштарханидов (или Джанидов), происходившей из рода астраханских ханов-чингизидов, породнившихся с Шейбанидами. Наиболее известным правителем этой династии был Абдулазиз-хан и особенно Субхан-Кули-хан, но подлинного культурного расцвета архитектура региона достигла при их преемниках: в этот период на площади Регистан в Самарканде рядом со старым медресе Улугбека были возведены медресе Шердор (1619–1636 гг., с характерным изображением тигров на портале) и медресе Тилля-Кари (1646–1660 гг., «золотое медресе»), завершившие формирование этого выдающегося архитектурного ансамбля. Одновременно государство сталкивалось с растущей внутренней нестабильностью: усиливалась власть местной кочевой и полукочевой знати (эмиров), ослабевал контроль центра над окраинами. В 1740-х гг. Бухарское ханство подверглось разорительному нашествию иранского правителя Надир-шаха, что ещё больше подорвало власть Аштарханидов. К середине XVIII в. династия фактически лишилась реальной власти, которая перешла к военачальникам из узбекского племени мангытов, что привело в 1756 г. к установлению новой Бухарской (Мангытской) династии эмиров.</t>
+          <t>После пресечения династии Шейбанидов в 1599 г. власть в Бухарском ханстве перешла к династии Аштарханидов (или Джанидов), происходившей из рода астраханских ханов-чингизидов, породнившихся с Шейбанидами. Наиболее известным правителем этой династии был Абдулазиз-хан и особенно Субхан-Кули-хан, но подлинного культурного расцвета архитектура региона достигла при их преемниках: в этот период на площади Регистан в Самарканде рядом со старым медресе Улугбека были возведены медресе Шердор (1619–1636 гг., с характерным изображением тигров на портале) и медресе Тилля-Кари (1646–1660 гг., «золотое медресе»; оба медресе возведены по заказу правителя Самарканда Ялангтуша Бахадура — Шердор при Имамкули-хане, Тилля-Кари при Абдулазиз-хане), завершившие формирование этого выдающегося архитектурного ансамбля. Одновременно государство сталкивалось с растущей внутренней нестабильностью: усиливалась власть местной кочевой и полукочевой знати (эмиров), ослабевал контроль центра над окраинами. В 1740-х гг. Бухарское ханство подверглось разорительному нашествию иранского правителя Надир-шаха, что ещё больше подорвало власть Аштарханидов. К середине XVIII в. династия фактически лишилась реальной власти, которая перешла к военачальникам из узбекского племени мангытов, что привело в 1756 г. к установлению новой Бухарской (Мангытской) династии эмиров.</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1599-yilda Shayboniylar sulolasi barham topgach, Buxoro xonligida hokimiyat Shayboniylar bilan qarindosh bo‘lgan Ashtraxan chingiziy xonlari urug‘idan bo‘lgan Ashtarxoniylar (yoki Joniylar) sulolasiga o‘tdi. Bu sulolaning eng mashhur hukmdorlari Abdulazizxon va ayniqsa Subxonqulixon bo‘lgan, biroq mintaqa me’morchiligi haqiqiy madaniy yuksalishga ularning voris avlodlari davrida erishdi: shu davrda Samarqanddagi Registon maydonida Ulug‘bekning eski madrasasi yonida Sherdor madrasasi (1619–1636-yillar, portalida yo‘lbarslar tasviri bilan) va Tillakori madrasasi (1646–1660-yillar, «oltin madrasa») qurilib, bu ajoyib me’moriy ansamblning shakllanishi yakunlandi. Shu bilan bir vaqtda davlat ichki beqarorlikning kuchayishiga duch keldi: mahalliy ko‘chmanchi va yarim ko‘chmanchi zodagonlar (amirlar) hokimiyati kuchaydi, markazning chekka hududlar ustidan nazorati zaiflashdi. 1740-yillarda Buxoro xonligi eron hukmdori Nodirshohning vayronkor bosqiniga uchradi, bu Ashtarxoniylar hokimiyatini yanada zaiflashtirdi. XVIII asr o‘rtasiga kelib sulola amalda haqiqiy hokimiyatdan mahrum bo‘ldi, hokimiyat o‘zbek mang‘it qabilasidan bo‘lgan sarkardalarga o‘tdi, bu esa 1756-yilda yangi Buxoro (Mang‘it) amirlar sulolasining o‘rnatilishiga olib keldi.</t>
+          <t>1599-yilda Shayboniylar sulolasi barham topgach, Buxoro xonligida hokimiyat Shayboniylar bilan qarindosh bo‘lgan Ashtraxan chingiziy xonlari urug‘idan bo‘lgan Ashtarxoniylar (yoki Joniylar) sulolasiga o‘tdi. Bu sulolaning eng mashhur hukmdorlari Abdulazizxon va ayniqsa Subxonqulixon bo‘lgan, biroq mintaqa me’morchiligi haqiqiy madaniy yuksalishga ularning voris avlodlari davrida erishdi: shu davrda Samarqanddagi Registon maydonida Ulug‘bekning eski madrasasi yonida Sherdor madrasasi (1619–1636-yillar, portalida yo‘lbarslar tasviri bilan) va Tillakori madrasasi (1646–1660-yillar, «oltin madrasa»; ikkala madrasa ham Samarqand hokimi Yalangto‘sh Bahodir buyurtmasi bilan qurilgan — Sherdor Imomqulixon, Tillakori Abdulazizxon davrida) qurilib, bu ajoyib me’moriy ansamblning shakllanishi yakunlandi. Shu bilan bir vaqtda davlat ichki beqarorlikning kuchayishiga duch keldi: mahalliy ko‘chmanchi va yarim ko‘chmanchi zodagonlar (amirlar) hokimiyati kuchaydi, markazning chekka hududlar ustidan nazorati zaiflashdi. 1740-yillarda Buxoro xonligi eron hukmdori Nodirshohning vayronkor bosqiniga uchradi, bu Ashtarxoniylar hokimiyatini yanada zaiflashtirdi. XVIII asr o‘rtasiga kelib sulola amalda haqiqiy hokimiyatdan mahrum bo‘ldi, hokimiyat o‘zbek mang‘it qabilasidan bo‘lgan sarkardalarga o‘tdi, bu esa 1756-yilda yangi Buxoro (Mang‘it) amirlar sulolasining o‘rnatilishiga olib keldi.</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>After the extinction of the Shaybanid dynasty in 1599, power in the Khanate of Bukhara passed to the Ashtarkhanid (or Janid) dynasty, descended from the Astrakhan Chinggisid khans, who had intermarried with the Shaybanids. The best-known rulers of this dynasty were Abdulaziz Khan and especially Subhan Quli Khan, but the region's architecture reached true cultural flowering under their successors: in this period, on the Registan Square in Samarkand, next to Ulugbek's old madrasa, the Sher-Dor madrasa (1619–1636, with its distinctive tigers depicted on the portal) and the Tilya-Kori madrasa (1646–1660, the «golden madrasa») were built, completing this outstanding architectural ensemble. At the same time the state faced growing internal instability: the power of local nomadic and semi-nomadic nobility (emirs) grew stronger, and central control over the periphery weakened. In the 1740s the Khanate of Bukhara suffered a devastating invasion by the Iranian ruler Nadir Shah, further undermining Ashtarkhanid power. By the mid-18th century the dynasty had effectively lost real power, which passed to commanders from the Uzbek Manghit tribe, leading in 1756 to the establishment of a new Bukharan (Manghit) dynasty of emirs.</t>
+          <t>After the extinction of the Shaybanid dynasty in 1599, power in the Khanate of Bukhara passed to the Ashtarkhanid (or Janid) dynasty, descended from the Astrakhan Chinggisid khans, who had intermarried with the Shaybanids. The best-known rulers of this dynasty were Abdulaziz Khan and especially Subhan Quli Khan, but the region's architecture reached true cultural flowering under their successors: in this period, on the Registan Square in Samarkand, next to Ulugbek's old madrasa, the Sher-Dor madrasa (1619–1636, with its distinctive tigers depicted on the portal) and the Tilya-Kori madrasa (1646–1660, the «golden madrasa»; both were commissioned by Yalangtush Bahadur, governor of Samarkand — Sher-Dor under Imam Quli Khan, Tilya-Kori under Abdulaziz Khan) were built, completing this outstanding architectural ensemble. At the same time the state faced growing internal instability: the power of local nomadic and semi-nomadic nobility (emirs) grew stronger, and central control over the periphery weakened. In the 1740s the Khanate of Bukhara suffered a devastating invasion by the Iranian ruler Nadir Shah, further undermining Ashtarkhanid power. By the mid-18th century the dynasty had effectively lost real power, which passed to commanders from the Uzbek Manghit tribe, leading in 1756 to the establishment of a new Bukharan (Manghit) dynasty of emirs.</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
